--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAB3C90-B34B-4EBE-A12B-2B368ECBA2D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068CAB6C-A921-4ED8-A456-E94E603642DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -61,9 +61,6 @@
     <t>GranteePOCContact__c</t>
   </si>
   <si>
-    <t>Automation SPI</t>
-  </si>
-  <si>
     <t>DropDown</t>
   </si>
   <si>
@@ -356,13 +353,16 @@
   </si>
   <si>
     <t>fieldSupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{users:Automation_SPI} </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,6 +373,13 @@
     <font>
       <sz val="9"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -397,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -406,6 +413,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,13 +731,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -746,29 +756,29 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -780,14 +790,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,81 +808,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -884,13 +894,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -901,70 +911,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -975,13 +985,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,70 +1002,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1066,13 +1076,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,323 +1093,323 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>51</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>59</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>63</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>65</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>67</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>69</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>71</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>73</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>75</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1410,14 +1420,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1428,103 +1438,103 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>89</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>90</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>91</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>92</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1536,12 +1546,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1549,48 +1559,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1601,14 +1611,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,48 +1629,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068CAB6C-A921-4ED8-A456-E94E603642DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58F6284-02A4-4EF1-8F61-F82553FA60DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -355,7 +355,7 @@
     <t>fieldSupportingCommentsQuestion1__c</t>
   </si>
   <si>
-    <t xml:space="preserve">{users:Automation_SPI} </t>
+    <t>Debra Clements</t>
   </si>
 </sst>
 </file>
@@ -377,9 +377,8 @@
       <family val="3"/>
     </font>
     <font>
-      <b/>
       <sz val="9.8000000000000007"/>
-      <color rgb="FF297BDE"/>
+      <color rgb="FF6A8759"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58F6284-02A4-4EF1-8F61-F82553FA60DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2287149E-B7FE-4C29-8AA9-AE4F27FCCCB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -355,14 +355,14 @@
     <t>fieldSupportingCommentsQuestion1__c</t>
   </si>
   <si>
-    <t>Debra Clements</t>
+    <t>SPI Automation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,10 +377,19 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FF6A8759"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -400,8 +409,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -412,11 +422,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -781,8 +790,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" tooltip="SPI Automation" display="https://lsc--qa--c.visualforce.com/0030r00000KHDtmAAH" xr:uid="{329E1606-5E73-498F-B12C-F4A3FE773863}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF815BD3-9809-47E1-82F7-D4AD3BE03AA6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2A1602-4291-4DEA-AA8D-477E9339DA6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4097" yWindow="1029" windowWidth="16457" windowHeight="8554" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -352,10 +352,10 @@
     <t>fieldSupportingCommentsQuestion1__c</t>
   </si>
   <si>
-    <t>Automation SPI</t>
-  </si>
-  <si>
     <t>Automation Runtime Award Desk</t>
+  </si>
+  <si>
+    <t>Automation SPI2</t>
   </si>
 </sst>
 </file>
@@ -731,13 +731,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -756,10 +756,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -767,10 +767,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -790,14 +790,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -808,7 +808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -819,7 +819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -830,7 +830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -841,7 +841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -852,7 +852,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -863,7 +863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -874,7 +874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -894,13 +894,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -922,7 +922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -933,7 +933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -944,7 +944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -955,7 +955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -966,7 +966,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -985,13 +985,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1076,13 +1076,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1420,14 +1420,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1546,12 +1546,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1583,22 +1583,22 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>21</v>
       </c>
@@ -1611,14 +1611,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2A1602-4291-4DEA-AA8D-477E9339DA6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40756AB0-D9A1-4564-BF55-8FD99595F705}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="111">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -58,15 +58,9 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>GranteePOCContact__c</t>
-  </si>
-  <si>
     <t>DropDown</t>
   </si>
   <si>
-    <t>MonitoringType__c</t>
-  </si>
-  <si>
     <t>Program &amp; Fiscal</t>
   </si>
   <si>
@@ -356,6 +350,21 @@
   </si>
   <si>
     <t>Automation SPI2</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldGranteePOCContact__c</t>
+  </si>
+  <si>
+    <t>fieldMonitoringType__c</t>
+  </si>
+  <si>
+    <t>fieldVisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>fieldVisitEndDateTime__c</t>
   </si>
 </sst>
 </file>
@@ -753,10 +762,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +773,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -810,10 +819,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -821,10 +830,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -832,57 +841,57 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -913,10 +922,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -924,10 +933,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -935,46 +944,46 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1015,10 +1024,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1026,46 +1035,46 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1098,10 +1107,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1109,10 +1118,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1120,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1131,10 +1140,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1142,10 +1151,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1153,10 +1162,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1164,10 +1173,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1175,10 +1184,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1186,10 +1195,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1197,10 +1206,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1208,10 +1217,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1219,10 +1228,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1230,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1241,10 +1250,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1252,10 +1261,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1263,10 +1272,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1274,10 +1283,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1285,10 +1294,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1296,10 +1305,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1307,10 +1316,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1318,10 +1327,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1329,10 +1338,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1340,10 +1349,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1351,10 +1360,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1362,10 +1371,10 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1373,10 +1382,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1384,10 +1393,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1395,10 +1404,10 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,10 +1415,10 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1443,10 +1452,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1454,10 +1463,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1465,10 +1474,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1476,10 +1485,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1487,10 +1496,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1498,10 +1507,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1509,10 +1518,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1520,10 +1529,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1531,10 +1540,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1564,7 +1573,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1572,35 +1581,35 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1631,46 +1640,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D5F17D-9586-483F-8098-07865DC1CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73146EF7-1B0C-43E6-9307-103F09201A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="115">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -341,9 +341,6 @@
     <t>fieldSiteVisitPurpose__c</t>
   </si>
   <si>
-    <t>fieldSourceSiteVisit__c</t>
-  </si>
-  <si>
     <t>fieldSupportingCommentsQuestion1__c</t>
   </si>
   <si>
@@ -360,6 +357,27 @@
   </si>
   <si>
     <t>Automation IND</t>
+  </si>
+  <si>
+    <t>VisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>VisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Pointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>SiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>SourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>SupportingCommentsQuestion1__c</t>
   </si>
 </sst>
 </file>
@@ -742,10 +760,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -767,7 +785,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -778,7 +796,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -801,9 +819,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0FA3F-2683-48C9-BD17-2A0A1746C85A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -826,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -837,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -859,11 +877,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -882,7 +900,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -893,7 +911,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -904,7 +922,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -915,7 +933,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -926,7 +944,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -937,7 +955,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -948,7 +966,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -963,7 +981,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -985,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -996,7 +1014,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1040,7 +1058,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1054,10 +1072,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1076,7 +1094,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1087,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1098,7 +1116,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1109,7 +1127,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1120,7 +1138,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1131,7 +1149,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1145,10 +1163,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1489,11 +1507,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1615,9 +1633,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1680,11 +1698,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73146EF7-1B0C-43E6-9307-103F09201A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D7D04F-B9F7-4DDB-8620-26B1B2D8A322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -332,28 +332,10 @@
     <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
   </si>
   <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldPointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>fieldSiteVisitPurpose__c</t>
-  </si>
-  <si>
-    <t>fieldSupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
     <t>Automation SPI3</t>
   </si>
   <si>
     <t>Automation Runtime Award Desk</t>
-  </si>
-  <si>
-    <t>fieldVisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>fieldVisitEndDateTime__c</t>
   </si>
   <si>
     <t>Automation IND</t>
@@ -463,9 +445,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -503,7 +485,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -609,7 +591,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -751,7 +733,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -760,10 +742,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -785,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -796,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -819,9 +801,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0FA3F-2683-48C9-BD17-2A0A1746C85A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -844,7 +826,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -855,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -877,11 +859,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -900,7 +882,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -911,7 +893,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -922,7 +904,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -933,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -944,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -955,7 +937,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -966,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -981,7 +963,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -1003,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1014,7 +996,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1025,7 +1007,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1036,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -1047,7 +1029,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -1058,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1072,10 +1054,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1094,7 +1076,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1105,7 +1087,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1116,7 +1098,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1127,7 +1109,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1138,7 +1120,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1149,7 +1131,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1163,10 +1145,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1507,11 +1489,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1633,9 +1615,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1698,11 +1680,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B2728A-BF8C-48C5-A5CB-024A5B8B3BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D5F17D-9586-483F-8098-07865DC1CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="3" r:id="rId2"/>
-    <sheet name="SourceError" sheetId="8" r:id="rId3"/>
-    <sheet name="InstructionError" sheetId="9" r:id="rId4"/>
-    <sheet name="Form Fields1" sheetId="5" r:id="rId5"/>
-    <sheet name="Form Fields" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet" sheetId="4" r:id="rId7"/>
-    <sheet name="Outcomes" sheetId="6" r:id="rId8"/>
+    <sheet name="Creation_IND" sheetId="10" r:id="rId2"/>
+    <sheet name="Edition" sheetId="3" r:id="rId3"/>
+    <sheet name="SourceError" sheetId="8" r:id="rId4"/>
+    <sheet name="InstructionError" sheetId="9" r:id="rId5"/>
+    <sheet name="Form Fields1" sheetId="5" r:id="rId6"/>
+    <sheet name="Form Fields" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet" sheetId="4" r:id="rId8"/>
+    <sheet name="Outcomes" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -76,12 +77,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>VisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>VisitEndDateTime__c</t>
-  </si>
-  <si>
     <t>RichText</t>
   </si>
   <si>
@@ -362,6 +357,9 @@
   </si>
   <si>
     <t>fieldVisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>Automation IND</t>
   </si>
 </sst>
 </file>
@@ -769,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -780,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -801,6 +799,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0FA3F-2683-48C9-BD17-2A0A1746C85A}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -826,7 +882,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -837,7 +893,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -848,10 +904,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -859,10 +915,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -870,10 +926,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -881,10 +937,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -892,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -928,8 +984,8 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
+      <c r="B2" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -939,8 +995,8 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
+      <c r="B3" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -951,10 +1007,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -962,10 +1018,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -973,10 +1029,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -984,10 +1040,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1019,8 +1075,8 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
+      <c r="B2" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1030,8 +1086,8 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
+      <c r="B3" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1042,21 +1098,21 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>103</v>
+      <c r="B5" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1064,10 +1120,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1075,10 +1131,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1086,7 +1142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1111,10 +1167,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1122,10 +1178,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1133,10 +1189,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1144,10 +1200,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1155,10 +1211,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1166,10 +1222,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1177,10 +1233,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1188,10 +1244,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1199,10 +1255,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1210,10 +1266,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1221,10 +1277,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1232,10 +1288,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1243,10 +1299,10 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1254,10 +1310,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1265,10 +1321,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1276,10 +1332,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1287,10 +1343,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1298,10 +1354,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1309,10 +1365,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1320,10 +1376,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1331,10 +1387,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1342,10 +1398,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1353,10 +1409,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1364,10 +1420,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1375,10 +1431,10 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1386,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1397,10 +1453,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1408,10 +1464,10 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1419,10 +1475,10 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1456,10 +1512,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1467,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1478,10 +1534,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1489,10 +1545,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1500,10 +1556,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1511,10 +1567,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1522,10 +1578,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1533,10 +1589,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1544,10 +1600,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1593,27 +1649,27 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1621,7 +1677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1644,46 +1700,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D5F17D-9586-483F-8098-07865DC1CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347D607F-D1D6-473B-82F9-23C3EE194F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="113">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -347,9 +347,6 @@
     <t>fieldSupportingCommentsQuestion1__c</t>
   </si>
   <si>
-    <t>Automation SPI3</t>
-  </si>
-  <si>
     <t>Automation Runtime Award Desk</t>
   </si>
   <si>
@@ -360,13 +357,28 @@
   </si>
   <si>
     <t>Automation IND</t>
+  </si>
+  <si>
+    <t>Department of Health</t>
+  </si>
+  <si>
+    <t>Victoria Leeds</t>
+  </si>
+  <si>
+    <t>Departmental description</t>
+  </si>
+  <si>
+    <t>Through Project Based Learning, students acquire real world skills, achieve academic success, and find purpose</t>
+  </si>
+  <si>
+    <t>At the request of the subrecipient</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +405,19 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -414,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -427,6 +452,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,9 +476,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -485,7 +516,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -591,7 +622,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -733,7 +764,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -742,10 +773,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -766,8 +797,8 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>105</v>
+      <c r="C2" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -777,8 +808,8 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>104</v>
+      <c r="C3" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -801,9 +832,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0FA3F-2683-48C9-BD17-2A0A1746C85A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -826,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -837,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -859,11 +890,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -882,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -893,7 +924,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -907,7 +938,7 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -918,7 +949,7 @@
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -951,7 +982,7 @@
         <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -963,7 +994,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -985,7 +1016,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -996,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1054,10 +1085,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1076,7 +1107,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1087,7 +1118,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1145,10 +1176,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1489,11 +1520,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1615,9 +1646,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1680,11 +1711,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D7D04F-B9F7-4DDB-8620-26B1B2D8A322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BF187C-55FB-4433-82FB-C566448E025A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -360,13 +360,16 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>Department of Health</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +396,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -414,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -427,6 +437,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,10 +755,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -766,8 +779,8 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>100</v>
+      <c r="C2" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -801,9 +814,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0FA3F-2683-48C9-BD17-2A0A1746C85A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -859,11 +872,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -963,7 +976,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -1054,10 +1067,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1145,10 +1158,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1489,11 +1502,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1615,9 +1628,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1680,11 +1693,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/DeskReview_Field_Values.xlsx
+++ b/src/main/resources/DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D7D04F-B9F7-4DDB-8620-26B1B2D8A322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F698BCE4-DA6A-436A-9D9A-40D46CDE8730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -332,9 +332,6 @@
     <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
   </si>
   <si>
-    <t>Automation SPI3</t>
-  </si>
-  <si>
     <t>Automation Runtime Award Desk</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>Deshka Kostova</t>
   </si>
 </sst>
 </file>
@@ -742,10 +742,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -778,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -801,9 +801,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0FA3F-2683-48C9-BD17-2A0A1746C85A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -826,7 +826,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -837,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -859,11 +859,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -882,7 +882,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -893,7 +893,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -904,7 +904,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -915,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -937,7 +937,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -963,7 +963,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A26CCC8-9D00-4BF3-A8AD-20D2DBFACF71}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -985,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1007,7 +1007,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1018,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -1029,7 +1029,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -1040,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1054,10 +1054,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB83CE-C8E5-44AF-AE3C-DF3141462411}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1076,7 +1076,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1087,7 +1087,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1098,7 +1098,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1120,7 +1120,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1131,7 +1131,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1145,10 +1145,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4F942-EBC7-4392-9497-9CD173C449CD}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1489,11 +1489,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEE61CD-3237-422A-82E8-CA9710108D17}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1615,9 +1615,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1680,11 +1680,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6B17DB-D82F-41EF-9E76-B6B556CE0B3E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
